--- a/data/trans_bre/P16A12-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A12-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,93</t>
+          <t>-1,5; 3,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 4,33</t>
+          <t>-2,53; 4,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,53</t>
+          <t>-4,33; 3,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 6,14</t>
+          <t>-1,44; 5,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 37,9</t>
+          <t>-11,56; 37,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 28,64</t>
+          <t>-13,35; 26,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 21,4</t>
+          <t>-20,11; 20,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 39,84</t>
+          <t>-7,25; 37,54</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,44; -0,26</t>
+          <t>-2,35; -0,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,64</t>
+          <t>-1,78; 0,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,03; -0,28</t>
+          <t>-3,12; -0,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -0,45</t>
+          <t>-4,49; -0,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,15; -10,42</t>
+          <t>-62,52; -9,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 22,07</t>
+          <t>-42,16; 21,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,56; -3,66</t>
+          <t>-48,12; -5,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,0; -17,72</t>
+          <t>-59,95; -18,28</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,32</t>
+          <t>-1,89; 1,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,62</t>
+          <t>-3,58; 0,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,13</t>
+          <t>-3,86; 0,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -1,76</t>
+          <t>-5,51; -1,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-76,87; 116,07</t>
+          <t>-76,26; 134,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-85,73; 45,19</t>
+          <t>-84,03; 58,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-78,29; 11,78</t>
+          <t>-79,26; 11,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,54; -35,6</t>
+          <t>-73,77; -34,45</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,62</t>
+          <t>-0,7; 1,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,51</t>
+          <t>-0,07; 2,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,88</t>
+          <t>-2,02; 0,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,71</t>
+          <t>-2,68; 0,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 31,06</t>
+          <t>-11,46; 32,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 38,51</t>
+          <t>-0,86; 36,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 11,5</t>
+          <t>-21,95; 12,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 8,53</t>
+          <t>-30,4; 7,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A12-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A12-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,79</t>
+          <t>-1,44; 3,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,02</t>
+          <t>-2,58; 4,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 3,47</t>
+          <t>-4,41; 3,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 5,91</t>
+          <t>-0,19; 6,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 37,04</t>
+          <t>-11,37; 34,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 26,55</t>
+          <t>-13,38; 28,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 20,6</t>
+          <t>-21,18; 18,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 37,54</t>
+          <t>-0,83; 46,84</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-3,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-43,8%</t>
+          <t>-42,5%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -0,28</t>
+          <t>-2,52; -0,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,65</t>
+          <t>-1,82; 0,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,12; -0,3</t>
+          <t>-2,99; -0,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -0,68</t>
+          <t>-4,31; -1,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,52; -9,27</t>
+          <t>-65,89; -9,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,16; 21,17</t>
+          <t>-43,38; 22,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,12; -5,53</t>
+          <t>-46,44; -4,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,95; -18,28</t>
+          <t>-51,77; -27,83</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,39</t>
+          <t>-3,45</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-58,19%</t>
+          <t>-57,58%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,44</t>
+          <t>-1,96; 1,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,76</t>
+          <t>-3,54; 0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,13</t>
+          <t>-4,19; -0,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; -1,77</t>
+          <t>-5,54; -1,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-76,26; 134,54</t>
+          <t>-73,56; 113,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,03; 58,38</t>
+          <t>-82,96; 57,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,26; 11,55</t>
+          <t>-79,12; 6,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,77; -34,45</t>
+          <t>-73,72; -35,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-14,97%</t>
+          <t>-14,49%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,67</t>
+          <t>-0,69; 1,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,48</t>
+          <t>-0,12; 2,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,93</t>
+          <t>-1,85; 0,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,68</t>
+          <t>-2,4; -0,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 32,72</t>
+          <t>-11,07; 29,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 36,18</t>
+          <t>-1,51; 35,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 12,31</t>
+          <t>-20,55; 10,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 7,87</t>
+          <t>-24,82; -3,2</t>
         </is>
       </c>
     </row>
